--- a/docs/students/9o..xlsx
+++ b/docs/students/9o..xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\María Alexandra\Listados Actualizados\LISTADOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\AgenteIA_Alexandra\docs\students\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EEAA696-EDA0-4DC3-A322-DB8A97FF797E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7D6926-46E6-468C-8056-0840B5E30440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,26 +37,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="119">
   <si>
     <t xml:space="preserve">CORREO MAMÁ </t>
   </si>
   <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>Correo institucional</t>
-  </si>
-  <si>
-    <t>Nombre mamá</t>
-  </si>
-  <si>
-    <t>Nombre papá</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORREO PAPÁ </t>
-  </si>
-  <si>
     <t xml:space="preserve">Alvarez Alvarez Isabella </t>
   </si>
   <si>
@@ -96,9 +81,6 @@
     <t>carlosgalicia26@hotmail.com</t>
   </si>
   <si>
-    <t>M*485258557497ay</t>
-  </si>
-  <si>
     <t>Carreño Castañeda Martin</t>
   </si>
   <si>
@@ -391,6 +373,27 @@
   </si>
   <si>
     <t>23AC0280@cac.edu.co</t>
+  </si>
+  <si>
+    <t>NOMBRE</t>
+  </si>
+  <si>
+    <t>CORREO INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>NOMBRE MAMÁ</t>
+  </si>
+  <si>
+    <t>NOMBRE  PAPÁ</t>
+  </si>
+  <si>
+    <t>CORREO PAPÁ</t>
+  </si>
+  <si>
+    <t>ID_DRIVE</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1odLpbR5jpl2Qf17hE0nwNbIF1OdTgv3o?usp=drive_link</t>
   </si>
 </sst>
 </file>
@@ -436,7 +439,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -460,13 +463,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
-      </left>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -476,7 +488,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -484,12 +496,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -831,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="31.375" customWidth="1"/>
@@ -840,463 +849,527 @@
     <col min="4" max="4" width="59.875" customWidth="1"/>
     <col min="5" max="5" width="28.375" customWidth="1"/>
     <col min="6" max="6" width="31.75" customWidth="1"/>
-    <col min="7" max="7" width="18.75" customWidth="1"/>
+    <col min="7" max="7" width="77.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="84.6" customHeight="1">
-      <c r="A1" s="8"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-    </row>
-    <row r="2" spans="1:7" ht="15">
-      <c r="A2" s="2" t="s">
+    <row r="1" spans="1:10" ht="15">
+      <c r="A1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="7"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="G2" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="B4" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
+      <c r="D4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="G4" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="C11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="C12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="C14" s="1"/>
+      <c r="D14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="C15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="1" t="s">
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="G20" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>98</v>
+      <c r="G21" s="3" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D5" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
-    <hyperlink ref="D6" r:id="rId2" display="cam0822@hotmail.com, bilipe1ster@gmail.com, camcl0822@gmail.com" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
-    <hyperlink ref="D13" r:id="rId3" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
-    <hyperlink ref="D15" r:id="rId4" xr:uid="{00000000-0004-0000-0300-000003000000}"/>
-    <hyperlink ref="D12" r:id="rId5" xr:uid="{00000000-0004-0000-0300-000004000000}"/>
-    <hyperlink ref="D3" r:id="rId6" xr:uid="{00000000-0004-0000-0300-000005000000}"/>
-    <hyperlink ref="F13" r:id="rId7" xr:uid="{00000000-0004-0000-0300-000006000000}"/>
-    <hyperlink ref="F5" r:id="rId8" xr:uid="{00000000-0004-0000-0300-000007000000}"/>
-    <hyperlink ref="F20" r:id="rId9" xr:uid="{00000000-0004-0000-0300-000008000000}"/>
-    <hyperlink ref="D20" r:id="rId10" xr:uid="{00000000-0004-0000-0300-000009000000}"/>
-    <hyperlink ref="D19" r:id="rId11" xr:uid="{00000000-0004-0000-0300-00000A000000}"/>
-    <hyperlink ref="F19" r:id="rId12" xr:uid="{00000000-0004-0000-0300-00000B000000}"/>
-    <hyperlink ref="D9" r:id="rId13" xr:uid="{00000000-0004-0000-0300-00000C000000}"/>
-    <hyperlink ref="F10" r:id="rId14" xr:uid="{00000000-0004-0000-0300-00000D000000}"/>
-    <hyperlink ref="F15" r:id="rId15" xr:uid="{00000000-0004-0000-0300-00000E000000}"/>
-    <hyperlink ref="F3" r:id="rId16" xr:uid="{00000000-0004-0000-0300-00000F000000}"/>
-    <hyperlink ref="F12" r:id="rId17" xr:uid="{00000000-0004-0000-0300-000010000000}"/>
-    <hyperlink ref="D10" r:id="rId18" xr:uid="{00000000-0004-0000-0300-000011000000}"/>
-    <hyperlink ref="B7" r:id="rId19" display="24AC0516@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0300-000012000000}"/>
-    <hyperlink ref="B8" r:id="rId20" display="26AC0023@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0300-000013000000}"/>
-    <hyperlink ref="F8" r:id="rId21" xr:uid="{00000000-0004-0000-0300-000014000000}"/>
-    <hyperlink ref="D8" r:id="rId22" xr:uid="{00000000-0004-0000-0300-000015000000}"/>
-    <hyperlink ref="B10" r:id="rId23" display="23AC0271@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0300-000016000000}"/>
-    <hyperlink ref="B11" r:id="rId24" display="23AC0272@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0300-000017000000}"/>
-    <hyperlink ref="D17" r:id="rId25" xr:uid="{00000000-0004-0000-0300-000018000000}"/>
-    <hyperlink ref="F17" r:id="rId26" xr:uid="{00000000-0004-0000-0300-000019000000}"/>
-    <hyperlink ref="D14" r:id="rId27" xr:uid="{00000000-0004-0000-0300-00001A000000}"/>
-    <hyperlink ref="D11" r:id="rId28" xr:uid="{00000000-0004-0000-0300-00001B000000}"/>
-    <hyperlink ref="F11" r:id="rId29" xr:uid="{00000000-0004-0000-0300-00001C000000}"/>
-    <hyperlink ref="D22" r:id="rId30" xr:uid="{00000000-0004-0000-0300-00001D000000}"/>
-    <hyperlink ref="F22" r:id="rId31" xr:uid="{00000000-0004-0000-0300-00001E000000}"/>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="D5" r:id="rId2" display="cam0822@hotmail.com, bilipe1ster@gmail.com, camcl0822@gmail.com" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="D12" r:id="rId3" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
+    <hyperlink ref="D14" r:id="rId4" xr:uid="{00000000-0004-0000-0300-000003000000}"/>
+    <hyperlink ref="D11" r:id="rId5" xr:uid="{00000000-0004-0000-0300-000004000000}"/>
+    <hyperlink ref="D2" r:id="rId6" xr:uid="{00000000-0004-0000-0300-000005000000}"/>
+    <hyperlink ref="F12" r:id="rId7" xr:uid="{00000000-0004-0000-0300-000006000000}"/>
+    <hyperlink ref="F4" r:id="rId8" xr:uid="{00000000-0004-0000-0300-000007000000}"/>
+    <hyperlink ref="F19" r:id="rId9" xr:uid="{00000000-0004-0000-0300-000008000000}"/>
+    <hyperlink ref="D19" r:id="rId10" xr:uid="{00000000-0004-0000-0300-000009000000}"/>
+    <hyperlink ref="D18" r:id="rId11" xr:uid="{00000000-0004-0000-0300-00000A000000}"/>
+    <hyperlink ref="F18" r:id="rId12" xr:uid="{00000000-0004-0000-0300-00000B000000}"/>
+    <hyperlink ref="D8" r:id="rId13" xr:uid="{00000000-0004-0000-0300-00000C000000}"/>
+    <hyperlink ref="F9" r:id="rId14" xr:uid="{00000000-0004-0000-0300-00000D000000}"/>
+    <hyperlink ref="F14" r:id="rId15" xr:uid="{00000000-0004-0000-0300-00000E000000}"/>
+    <hyperlink ref="F2" r:id="rId16" xr:uid="{00000000-0004-0000-0300-00000F000000}"/>
+    <hyperlink ref="F11" r:id="rId17" xr:uid="{00000000-0004-0000-0300-000010000000}"/>
+    <hyperlink ref="D9" r:id="rId18" xr:uid="{00000000-0004-0000-0300-000011000000}"/>
+    <hyperlink ref="B6" r:id="rId19" display="24AC0516@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0300-000012000000}"/>
+    <hyperlink ref="B7" r:id="rId20" display="26AC0023@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0300-000013000000}"/>
+    <hyperlink ref="F7" r:id="rId21" xr:uid="{00000000-0004-0000-0300-000014000000}"/>
+    <hyperlink ref="D7" r:id="rId22" xr:uid="{00000000-0004-0000-0300-000015000000}"/>
+    <hyperlink ref="B9" r:id="rId23" display="23AC0271@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0300-000016000000}"/>
+    <hyperlink ref="B10" r:id="rId24" display="23AC0272@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0300-000017000000}"/>
+    <hyperlink ref="D16" r:id="rId25" xr:uid="{00000000-0004-0000-0300-000018000000}"/>
+    <hyperlink ref="F16" r:id="rId26" xr:uid="{00000000-0004-0000-0300-000019000000}"/>
+    <hyperlink ref="D13" r:id="rId27" xr:uid="{00000000-0004-0000-0300-00001A000000}"/>
+    <hyperlink ref="D10" r:id="rId28" xr:uid="{00000000-0004-0000-0300-00001B000000}"/>
+    <hyperlink ref="F10" r:id="rId29" xr:uid="{00000000-0004-0000-0300-00001C000000}"/>
+    <hyperlink ref="D21" r:id="rId30" xr:uid="{00000000-0004-0000-0300-00001D000000}"/>
+    <hyperlink ref="F21" r:id="rId31" xr:uid="{00000000-0004-0000-0300-00001E000000}"/>
+    <hyperlink ref="G2" r:id="rId32" xr:uid="{1145EDA2-62AD-4C03-82F5-EA017DE3C61C}"/>
+    <hyperlink ref="G3:G13" r:id="rId33" display="https://drive.google.com/drive/folders/1odLpbR5jpl2Qf17hE0nwNbIF1OdTgv3o?usp=drive_link" xr:uid="{DA3D6BC1-DF4F-4852-AA23-9D76286052B4}"/>
+    <hyperlink ref="G14:G19" r:id="rId34" display="https://drive.google.com/drive/folders/1odLpbR5jpl2Qf17hE0nwNbIF1OdTgv3o?usp=drive_link" xr:uid="{C7980CF8-8551-4E74-B32A-E2B481C15987}"/>
+    <hyperlink ref="G21" r:id="rId35" xr:uid="{D135A08E-5E95-4C41-BFEC-B3D3BB1D4C6E}"/>
+    <hyperlink ref="G20" r:id="rId36" xr:uid="{6B6A1060-4826-40FF-A3B1-ADE8DCE28D43}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010033786E0F47F2E4479E1418699C7D1887" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="8889b9d8e9583677ca2221be300ac5d5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b44af97c-a663-43df-bc64-dfb44812992d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8c5274dc35b9ea6c79ecd381a4eab1a6" ns2:_="">
     <xsd:import namespace="b44af97c-a663-43df-bc64-dfb44812992d"/>
@@ -1434,7 +1507,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1443,13 +1516,16 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35073413-9516-4B73-8842-99BBF230AC45}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{196073E8-6B75-4A3D-94ED-1A629E1F09BE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1467,19 +1543,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BBBEA71-C632-4AE8-B7C8-3F289DADFCB3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35073413-9516-4B73-8842-99BBF230AC45}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>